--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-Reply.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-Reply.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2350" uniqueCount="421">
   <si>
     <t>Property</t>
   </si>
@@ -499,6 +499,13 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Communication.meta.tag</t>
   </si>
   <si>
@@ -668,6 +675,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Communication.instantiatesCanonical</t>
   </si>
   <si>
@@ -681,6 +691,9 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -722,7 +735,14 @@
     <t>Hat die Form 'Task/{{PrescriptionID}}'</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.basedOn.id</t>
@@ -819,6 +839,9 @@
     <t>Part of this action.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -894,6 +917,9 @@
     <t>Event.statusReason</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -946,6 +972,9 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1042,7 +1071,7 @@
     <t>The time when this communication was sent.</t>
   </si>
   <si>
-    <t>Wird vom E-Rezept-Server gesetzt. Ein Client hat diesen Wert daher immer verfügbar.</t>
+    <t>Wird vom TIFlow-Server gesetzt. Ein Client hat diesen Wert daher immer verfügbar.</t>
   </si>
   <si>
     <t>Event.occurrence[x] {Invariant: maps to period.start}</t>
@@ -1123,11 +1152,11 @@
     <t>Die Entität (z. B. Person, Organisation), die Quelle der Kommunikation war.</t>
   </si>
   <si>
-    <t>Nachrichtenabsender — wird vom E-Rezept-Server unter Verwendung der AuthN-Credential des Clients gesetzt.
+    <t>Nachrichtenabsender — wird vom TIFlow-Server gesetzt.
 Die Entität (z. B. Person, Organisation), die Quelle der Kommunikation war.</t>
   </si>
   <si>
-    <t>Wird vom E-Rezept-Server unter Verwendung der AuthN-Credential des Clients gesetzt.</t>
+    <t>Wird vom TIFlow-Server gesetzt.</t>
   </si>
   <si>
     <t>Communication.sender.id</t>
@@ -1223,9 +1252,6 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Erweiterungen werden immer (mindestens) nach url gesliced.</t>
-  </si>
-  <si>
     <t>Communication.payload.extension:OfferedSupplyOptions</t>
   </si>
   <si>
@@ -1245,10 +1271,6 @@
     <t>Sowohl Patient als auch Apotheke können ihre Lieferoptionen oder Angebote für die Abgabe von Medikamenten angeben.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Communication.payload.extension:AvailabilityStatus</t>
   </si>
   <si>
@@ -1304,7 +1326,13 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
+  </si>
+  <si>
     <t>Event.note</t>
+  </si>
+  <si>
+    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1656,7 +1684,7 @@
     <col min="26" max="26" width="52.72265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="49.6328125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.7421875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1665,7 +1693,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2336,7 +2364,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -2355,7 +2383,7 @@
         <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>77</v>
@@ -2447,7 +2475,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>122</v>
       </c>
@@ -2466,7 +2494,7 @@
         <v>87</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>77</v>
@@ -2989,7 +3017,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
@@ -3001,15 +3029,15 @@
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3035,13 +3063,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3067,13 +3095,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3091,7 +3119,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3100,7 +3128,7 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>99</v>
@@ -3112,15 +3140,15 @@
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3146,13 +3174,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3202,7 +3230,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3228,10 +3256,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3254,16 +3282,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3289,13 +3317,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3313,7 +3341,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3339,14 +3367,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3365,16 +3393,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3424,7 +3452,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3445,19 +3473,19 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3476,16 +3504,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3535,7 +3563,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3556,15 +3584,15 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3593,7 +3621,7 @@
         <v>109</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>111</v>
@@ -3634,19 +3662,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3667,15 +3695,15 @@
         <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3701,16 +3729,16 @@
         <v>108</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3747,19 +3775,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3780,15 +3808,15 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3811,19 +3839,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3872,7 +3900,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3881,27 +3909,27 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>77</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3924,15 +3952,17 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3981,7 +4011,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3996,21 +4026,21 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4036,13 +4066,13 @@
         <v>129</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4092,7 +4122,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4107,25 +4137,25 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4144,16 +4174,16 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4203,7 +4233,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4212,27 +4242,27 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4338,10 +4368,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4449,10 +4479,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4478,13 +4508,13 @@
         <v>101</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4534,7 +4564,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4543,7 +4573,7 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>99</v>
@@ -4555,15 +4585,15 @@
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4589,13 +4619,13 @@
         <v>129</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4624,10 +4654,10 @@
         <v>151</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4645,7 +4675,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4666,15 +4696,15 @@
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4697,16 +4727,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4756,7 +4786,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4765,7 +4795,7 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
@@ -4777,15 +4807,15 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4811,13 +4841,13 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4867,7 +4897,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4888,19 +4918,19 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4919,15 +4949,17 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4976,7 +5008,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4985,27 +5017,27 @@
         <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5028,15 +5060,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5085,7 +5119,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5094,10 +5128,10 @@
         <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
@@ -5106,15 +5140,15 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5137,16 +5171,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5154,7 +5188,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>77</v>
@@ -5172,31 +5206,31 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="Z32" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>87</v>
@@ -5211,10 +5245,10 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5222,14 +5256,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5248,16 +5282,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5283,31 +5317,31 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="Z33" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5316,27 +5350,27 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5359,16 +5393,16 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5394,13 +5428,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5418,7 +5452,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5427,7 +5461,7 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>99</v>
@@ -5436,18 +5470,18 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5470,23 +5504,23 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q35" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="R35" t="s" s="2">
         <v>77</v>
@@ -5507,13 +5541,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5531,7 +5565,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5549,7 +5583,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5557,10 +5591,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5583,15 +5617,17 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5616,13 +5652,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5640,7 +5676,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5649,7 +5685,7 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>99</v>
@@ -5661,19 +5697,19 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5692,15 +5728,17 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5749,7 +5787,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5758,27 +5796,27 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5801,16 +5839,16 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5836,13 +5874,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5860,7 +5898,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5869,7 +5907,7 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
@@ -5878,18 +5916,18 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5912,16 +5950,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5971,7 +6009,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5980,27 +6018,27 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6023,16 +6061,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6082,7 +6120,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6091,27 +6129,27 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6134,16 +6172,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6193,7 +6231,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6208,10 +6246,10 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6219,10 +6257,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6245,16 +6283,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6304,7 +6342,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6319,10 +6357,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6330,10 +6368,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6356,16 +6394,16 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6415,7 +6453,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6424,27 +6462,27 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6550,10 +6588,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6661,10 +6699,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6690,13 +6728,13 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6746,7 +6784,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6755,7 +6793,7 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
@@ -6767,15 +6805,15 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6801,13 +6839,13 @@
         <v>129</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6836,10 +6874,10 @@
         <v>151</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6857,7 +6895,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6878,15 +6916,15 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6909,16 +6947,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6968,7 +7006,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6977,7 +7015,7 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
@@ -6989,15 +7027,15 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7023,13 +7061,13 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7079,7 +7117,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7100,15 +7138,15 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7131,16 +7169,16 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7190,7 +7228,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7199,27 +7237,27 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7325,10 +7363,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7436,10 +7474,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7465,13 +7503,13 @@
         <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7521,7 +7559,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7530,7 +7568,7 @@
         <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>99</v>
@@ -7542,15 +7580,15 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7576,13 +7614,13 @@
         <v>129</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7611,10 +7649,10 @@
         <v>151</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7632,7 +7670,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7653,15 +7691,15 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7684,16 +7722,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7743,7 +7781,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7752,7 +7790,7 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>99</v>
@@ -7764,15 +7802,15 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7798,13 +7836,13 @@
         <v>101</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7854,7 +7892,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7875,15 +7913,15 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7906,16 +7944,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7941,13 +7979,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -7965,7 +8003,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7974,27 +8012,27 @@
         <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8017,15 +8055,17 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8074,7 +8114,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8083,27 +8123,27 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8126,13 +8166,13 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8183,7 +8223,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8192,7 +8232,7 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>99</v>
@@ -8204,15 +8244,15 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8318,10 +8358,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8347,10 +8387,10 @@
         <v>108</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8392,7 +8432,7 @@
         <v>112</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>386</v>
+        <v>113</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>77</v>
@@ -8427,13 +8467,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>77</v>
@@ -8455,16 +8495,16 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8523,7 +8563,7 @@
         <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>116</v>
@@ -8540,13 +8580,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>77</v>
@@ -8568,13 +8608,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8634,7 +8674,7 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>116</v>
@@ -8651,14 +8691,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8680,16 +8720,16 @@
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -8738,7 +8778,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8759,15 +8799,15 @@
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8793,13 +8833,13 @@
         <v>101</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8849,7 +8889,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>87</v>
@@ -8858,7 +8898,7 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>99</v>
@@ -8870,15 +8910,15 @@
         <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8901,15 +8941,17 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8958,7 +9000,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -8967,19 +9009,19 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-Reply.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Communication-Reply.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
